--- a/Result/profitability/4939.xlsx
+++ b/Result/profitability/4939.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.007499999999999972</v>
+        <v>0.01500000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>21.23375</v>
+        <v>21.74375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04750000000000004</v>
+        <v>0.09625000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>21.44875</v>
+        <v>22.71</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.115</v>
+        <v>0.14375</v>
       </c>
       <c r="N4" t="n">
-        <v>21.05375</v>
+        <v>21.3975</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2</v>
+        <v>0.33875</v>
       </c>
       <c r="N5" t="n">
-        <v>22.05625</v>
+        <v>23.10625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>99.2</v>
@@ -1137,10 +1137,10 @@
         <v>0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36</v>
+        <v>0.3675</v>
       </c>
       <c r="N6" t="n">
-        <v>22.98125</v>
+        <v>23.39375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3350000000000001</v>
+        <v>0.35875</v>
       </c>
       <c r="N7" t="n">
-        <v>22.51875</v>
+        <v>23.08</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>435</v>
+      </c>
+      <c r="D69" t="n">
+        <v>320</v>
+      </c>
+      <c r="E69" t="n">
+        <v>115</v>
+      </c>
+      <c r="F69" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G69" t="n">
+        <v>39</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>43</v>
+      </c>
+      <c r="K69" t="n">
+        <v>28</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.01375000000000003</v>
+      </c>
+      <c r="N69" t="n">
+        <v>22.53375</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.07627711686494054</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-1.353658536585366</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>8.399999999999999</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
